--- a/Provodnik/_шаблоны/Ф6_ost.xlsx
+++ b/Provodnik/_шаблоны/Ф6_ost.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -257,6 +257,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -706,7 +709,7 @@
       <c r="B8" s="12"/>
       <c r="C8" s="11"/>
       <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="E8" s="11"/>
       <c r="F8" s="12"/>
       <c r="G8" s="11"/>
       <c r="H8" s="12"/>
@@ -719,7 +722,7 @@
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="E9" s="21"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
